--- a/assets/templates/template-sales.xlsx
+++ b/assets/templates/template-sales.xlsx
@@ -2326,7 +2326,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. الأعمدة النصية (الفرع، القسم، القناة) تصير فلاتر وتقسيمات في الداش بورد.</v>
+        <v>3. الأعمدة النصية (الفرع، القسم، القناة) تصير فلاتر وتقسيمات في لوحة التحكم.</v>
       </c>
     </row>
     <row r="6">

--- a/assets/templates/template-sales.xlsx
+++ b/assets/templates/template-sales.xlsx
@@ -2326,7 +2326,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. الأعمدة النصية (الفرع، القسم، القناة) تصير فلاتر وتقسيمات في لوحة التحكم.</v>
+        <v>3. الأعمدة النصية (الفرع، القسم، القناة) تصير فلاتر وتقسيمات في لوحة المؤشرات.</v>
       </c>
     </row>
     <row r="6">
